--- a/Dev_GNC/TableData/Proto/Proto_PawnDataTable.xlsx
+++ b/Dev_GNC/TableData/Proto/Proto_PawnDataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityProjects\CardGame\CardGameTable\Table\Proto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealProjects\ProjectGNC\Dev_GNC\TableData\Proto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D2F953-FA75-49E5-9CDA-6FE72677C352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB7BF6D-9AC6-4B9D-AE81-E232C9EDDD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="_Schema" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="42">
   <si>
     <t>MessageName</t>
   </si>
@@ -148,6 +148,10 @@
   </si>
   <si>
     <t>정확도(만분율)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>classref:CardGameActor</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -436,6 +440,9 @@
   </sheetPr>
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -686,7 +693,7 @@
         <v>33</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="D15" s="1">
         <v>14</v>

--- a/Dev_GNC/TableData/Proto/Proto_PawnDataTable.xlsx
+++ b/Dev_GNC/TableData/Proto/Proto_PawnDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealProjects\ProjectGNC\Dev_GNC\TableData\Proto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB7BF6D-9AC6-4B9D-AE81-E232C9EDDD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0B87BD-2A98-4718-A95F-669682DFA366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42480" yWindow="2760" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="_Schema" sheetId="1" r:id="rId1"/>
@@ -121,9 +121,6 @@
     <t>시야</t>
   </si>
   <si>
-    <t>prefabPath</t>
-  </si>
-  <si>
     <t>리소스경로</t>
   </si>
   <si>
@@ -151,7 +148,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>classref:CardGameActor</t>
+    <t>classref:ACardGameActor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>actorLink</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -656,24 +657,24 @@
     </row>
     <row r="13" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" s="1">
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>8</v>
@@ -685,15 +686,15 @@
         <v>9</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15" s="1">
         <v>14</v>
@@ -702,7 +703,7 @@
         <v>9</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">

--- a/Dev_GNC/TableData/Proto/Proto_PawnDataTable.xlsx
+++ b/Dev_GNC/TableData/Proto/Proto_PawnDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealProjects\ProjectGNC\Dev_GNC\TableData\Proto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0B87BD-2A98-4718-A95F-669682DFA366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834C08A6-92CF-4770-A4C0-D38067E5FB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42480" yWindow="2760" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39180" yWindow="2460" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="_Schema" sheetId="1" r:id="rId1"/>
@@ -64,9 +64,6 @@
     <t>Alias</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>이름</t>
   </si>
   <si>
@@ -153,6 +150,10 @@
   </si>
   <si>
     <t>actorLink</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>nameAlias</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -504,7 +505,7 @@
     </row>
     <row r="4" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>12</v>
@@ -516,15 +517,15 @@
         <v>9</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -533,12 +534,12 @@
         <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>8</v>
@@ -550,12 +551,12 @@
         <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>8</v>
@@ -567,12 +568,12 @@
         <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>8</v>
@@ -584,46 +585,46 @@
         <v>9</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="1">
-        <v>8</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="1">
-        <v>9</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>8</v>
@@ -635,12 +636,12 @@
         <v>9</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>8</v>
@@ -652,29 +653,29 @@
         <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" s="1">
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>8</v>
@@ -686,15 +687,15 @@
         <v>9</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" s="1">
         <v>14</v>
@@ -703,7 +704,7 @@
         <v>9</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
